--- a/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
+++ b/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
@@ -1714,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"المستخلصات": [["232/2025/1/36", "PO01", "8", "حى الحدق - سنترال رابعة / 6 كبائن", "3027947.36", "3451859.98", "تم الصرف", "", "", "", ""]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
+++ b/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
@@ -1600,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1652,52 +1652,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>• نوع الأعمال بيتعرف من اسم المسار: كهرب ← أعمال كهربية، تخطيط ← تخطيط ورسومات، صيانة ← صيانة مدني، متكامل ← أعمال متكاملة، وغير كده أعمال مدنية.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>قواعد عامة لكل القوالب</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
+          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
           <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
         </is>

--- a/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
+++ b/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
@@ -559,27 +559,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>المبلغ غير شامل *</t>
+          <t>المبلغ غير شامل الضريبة *</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>المبلغ شامل</t>
+          <t>المبلغ شامل الضريبة</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>المحطة الحالية *</t>
+          <t>مرحلة الاعتماد الحالية *</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>في المحطة من تاريخ</t>
+          <t>في المرحلة منذ تاريخ</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>الماسك الحالي</t>
+          <t>الجهة الحالية (الاسم)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>تم الصرف</t>
+          <t>تم السداد</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -1577,16 +1577,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F3:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="قيمة غير مسموحة" error="اختار من القائمة" type="list">
-      <formula1>"الشركة,مشرف التنفيذ,مدير التنفيذ,المدير العام,الشئون الفنية,التخطيط,رئيس القطاع,المخازن والمشتريات,المالية,تم الصرف,بانتظار أمر التكليف"</formula1>
+    <dataValidation sqref="G3:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="قيمة غير مسموحة" error="يرجى الاختيار من القائمة" type="list">
+      <formula1>"المقاول,مشرف التنفيذ,مدير التنفيذ,المدير العام,الشئون الفنية,التخطيط,رئيس القطاع,المخازن والمشتريات,الإدارة المالية,تم السداد,بانتظار أمر التكليف"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="لازم تاريخ (يوم/شهر/سنة)" type="date" operator="greaterThan">
+    <dataValidation sqref="H3:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="يجب إدخال تاريخ بصيغة يوم/شهر/سنة" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -1609,21 +1609,21 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>قالب ترحيل المستخلصات الحالية</t>
+          <t>نموذج ترحيل بيانات المستخلصات الحالية</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>الغرض: إدخال المستخلصات الموجودة قبل تشغيل المنظومة (من ملفات الموقف).</t>
+          <t>الغرض: إدخال المستخلصات القائمة قبل تشغيل المنظومة (من ملفات الموقف).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>مين بيرفعه: فريق المتابعة PMO — مرة واحدة عند التشغيل.</t>
+          <t>الجهة المسؤولة عن الرفع: مكتب إدارة المشروعات (PMO) — مرة واحدة عند بدء التشغيل.</t>
         </is>
       </c>
     </row>
@@ -1633,28 +1633,28 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>• المستخلصات المرحّلة بتظهر بعلامة "مرحّل" ومن غير بنود تفصيلية.</t>
+          <t>• تظهر المستخلصات المُرحَّلة بعلامة "مُرحَّل" دون بنود تفصيلية.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>• تاريخ المحطة بيستخدم عشان عداد الـ SLA يبدأ صح.</t>
+          <t>• يُستخدم تاريخ دخول المرحلة لضبط بداية احتساب المدة المستهدفة (SLA).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>• نوع الأعمال بيتعرف من اسم المسار: كهرب ← أعمال كهربية، تخطيط ← تخطيط ورسومات، صيانة ← صيانة مدني، متكامل ← أعمال متكاملة، وغير كده أعمال مدنية.</t>
+          <t>• يُستدل على نوع الأعمال من اسم المسار: كهرب ← أعمال كهربية، تخطيط ← تخطيط ورسومات، صيانة ← صيانة مدني، متكامل ← أعمال متكاملة، وفيما عدا ذلك أعمال مدنية.</t>
         </is>
       </c>
     </row>
@@ -1664,49 +1664,49 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"المستخلصات": [["232/2025/1/36", "PO01", "8", "حى الحدق - سنترال رابعة / 6 كبائن", "3027947.36", "3451859.98", "تم الصرف", "", "", "", ""]]}</t>
+          <t>{"المستخلصات": [["232/2025/1/36", "PO01", "8", "حى الحدق - سنترال رابعة / 6 كبائن", "3027947.36", "3451859.98", "تم السداد", "", "", "", ""]]}</t>
         </is>
       </c>
     </row>

--- a/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
+++ b/apps/web/public/templates/11_المستخلصات_السابقة.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>حى الحدق - سنترال رابعة / 6 كبائن</t>
+          <t>مثال — حى الحدق - سنترال رابعة / 6 كبائن</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"المستخلصات": [["232/2025/1/36", "PO01", "8", "حى الحدق - سنترال رابعة / 6 كبائن", "3027947.36", "3451859.98", "تم السداد", "", "", "", ""]]}</t>
+          <t>{"المستخلصات": [["232/2025/1/36", "PO01", "8", "مثال — حى الحدق - سنترال رابعة / 6 كبائن", "3027947.36", "3451859.98", "تم السداد", "", "", "", ""]]}</t>
         </is>
       </c>
     </row>
